--- a/data/trans_orig/P70C1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P70C1_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si vuelven demasiado cansados a casa como para hacer las tareas domésticas necesarias en 2023</t>
+          <t>Población según si vuelven demasiado cansados a casa como para hacer las tareas domésticas necesarias en 2023 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11907</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38128</t>
+          <t>37197</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18745</t>
+          <t>18343</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40987</t>
+          <t>41338</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34668</t>
+          <t>35614</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69625</t>
+          <t>70282</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15592</t>
+          <t>14675</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47244</t>
+          <t>45283</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15797</t>
+          <t>15243</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22122</t>
+          <t>22603</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56729</t>
+          <t>57370</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14283</t>
+          <t>13298</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24489</t>
+          <t>24696</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32403</t>
+          <t>34088</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28738</t>
+          <t>29356</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7860</t>
+          <t>7848</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25046</t>
+          <t>25233</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15248</t>
+          <t>15516</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45122</t>
+          <t>43595</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8796</t>
+          <t>9088</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35553</t>
+          <t>34687</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21105</t>
+          <t>19635</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17703</t>
+          <t>17787</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46428</t>
+          <t>46847</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12718</t>
+          <t>12613</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17082</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90800</t>
+          <t>88907</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134309</t>
+          <t>132652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>103839</t>
+          <t>106953</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>251369</t>
+          <t>257755</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>211960</t>
+          <t>212834</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>392784</t>
+          <t>405359</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>57,65%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41145</t>
+          <t>41715</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>75795</t>
+          <t>74934</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28224</t>
+          <t>28512</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76841</t>
+          <t>76260</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>77379</t>
+          <t>78536</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>138041</t>
+          <t>136497</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27122</t>
+          <t>26068</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54790</t>
+          <t>55706</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12353</t>
+          <t>12007</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38023</t>
+          <t>38724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43772</t>
+          <t>44143</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85909</t>
+          <t>85111</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49757</t>
+          <t>49976</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88864</t>
+          <t>88682</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21171</t>
+          <t>20736</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62736</t>
+          <t>60800</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77775</t>
+          <t>75985</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>136889</t>
+          <t>138992</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43323</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80711</t>
+          <t>80412</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25708</t>
+          <t>22629</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>69814</t>
+          <t>67583</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>74956</t>
+          <t>76886</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>134595</t>
+          <t>136783</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10728</t>
+          <t>11017</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>35029</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31993</t>
+          <t>31067</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26047</t>
+          <t>24972</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57050</t>
+          <t>56303</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>128365</t>
+          <t>129885</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>170268</t>
+          <t>171703</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72985</t>
+          <t>73385</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>100298</t>
+          <t>100356</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>207474</t>
+          <t>210109</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>259894</t>
+          <t>261427</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54834</t>
+          <t>53018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86992</t>
+          <t>83868</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49874</t>
+          <t>51343</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71805</t>
+          <t>74037</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>112345</t>
+          <t>111628</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>150328</t>
+          <t>149072</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49767</t>
+          <t>50675</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>79136</t>
+          <t>80592</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30353</t>
+          <t>30595</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50138</t>
+          <t>50866</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85660</t>
+          <t>86373</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>122207</t>
+          <t>122954</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72402</t>
+          <t>70570</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>108595</t>
+          <t>107157</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>47014</t>
+          <t>46933</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>70291</t>
+          <t>70991</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>126861</t>
+          <t>124451</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>167972</t>
+          <t>168863</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44843</t>
+          <t>45819</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>75087</t>
+          <t>76126</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56593</t>
+          <t>57051</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82328</t>
+          <t>81501</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>108947</t>
+          <t>108288</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>148400</t>
+          <t>146843</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18954</t>
+          <t>19334</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40204</t>
+          <t>40580</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>28856</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47816</t>
+          <t>48890</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>53812</t>
+          <t>54388</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>82290</t>
+          <t>84514</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>236172</t>
+          <t>239915</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>611936</t>
+          <t>611301</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>120883</t>
+          <t>121607</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>227493</t>
+          <t>231035</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>380491</t>
+          <t>376925</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>866562</t>
+          <t>847683</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>70,53%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>46039</t>
+          <t>36289</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>181612</t>
+          <t>177137</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>61086</t>
+          <t>59503</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>95438</t>
+          <t>94108</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>99806</t>
+          <t>107147</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>253709</t>
+          <t>255082</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>19543</t>
+          <t>19665</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>85873</t>
+          <t>81178</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>37156</t>
+          <t>36573</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>61946</t>
+          <t>61556</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>52531</t>
+          <t>53566</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>134651</t>
+          <t>135497</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34901</t>
+          <t>36526</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>134432</t>
+          <t>133099</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>46639</t>
+          <t>46110</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>74489</t>
+          <t>75332</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>75195</t>
+          <t>73329</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>192589</t>
+          <t>193815</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19962</t>
+          <t>21618</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>91471</t>
+          <t>89118</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>48861</t>
+          <t>48288</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>77608</t>
+          <t>78664</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>61751</t>
+          <t>63875</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>160999</t>
+          <t>161719</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>10647</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>53025</t>
+          <t>51964</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>32680</t>
+          <t>33379</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>62201</t>
+          <t>61753</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>39749</t>
+          <t>39102</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>106289</t>
+          <t>105415</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>81391</t>
+          <t>80432</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>111418</t>
+          <t>111549</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>38976</t>
+          <t>40246</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>56971</t>
+          <t>57325</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>126116</t>
+          <t>126783</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>160646</t>
+          <t>161653</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>48895</t>
+          <t>46839</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>72744</t>
+          <t>72585</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>33091</t>
+          <t>33466</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>49508</t>
+          <t>50944</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>86824</t>
+          <t>84949</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>117460</t>
+          <t>118210</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>22772</t>
+          <t>23299</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>41844</t>
+          <t>42306</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>18892</t>
+          <t>19093</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>32479</t>
+          <t>32431</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>45248</t>
+          <t>45638</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>68924</t>
+          <t>68263</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>36618</t>
+          <t>35901</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>60191</t>
+          <t>59934</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>29614</t>
+          <t>29734</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>47000</t>
+          <t>46680</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>72710</t>
+          <t>72466</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>101539</t>
+          <t>101278</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>34357</t>
+          <t>34173</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>55786</t>
+          <t>58159</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>23704</t>
+          <t>23645</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>39527</t>
+          <t>38545</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>62679</t>
+          <t>62423</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>90523</t>
+          <t>90237</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12795</t>
+          <t>14016</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>29683</t>
+          <t>31930</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>18682</t>
+          <t>17604</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>31919</t>
+          <t>31353</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>35694</t>
+          <t>36176</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>59181</t>
+          <t>57333</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -4705,12 +4705,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>11491</t>
+          <t>11291</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>9521</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>17961</t>
+          <t>17954</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,6%</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4833,12 +4833,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>10522</t>
+          <t>10816</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>622</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>974</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5044,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>7756</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>589</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>580</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>7667</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -5500,97 +5500,97 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
           <t>1598</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="V46" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O46" s="2" t="inlineStr">
+      <c r="W46" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>1598</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>1598</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
     </row>
@@ -5613,97 +5613,97 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="V47" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O47" s="2" t="inlineStr">
+      <c r="W47" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W47" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -5726,97 +5726,97 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr">
+      <c r="W48" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W48" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -5839,97 +5839,97 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="V49" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O49" s="2" t="inlineStr">
+      <c r="W49" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T49" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U49" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W49" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -5952,97 +5952,97 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="V50" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="W50" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W50" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -6065,97 +6065,97 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
+      <c r="V51" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O51" s="2" t="inlineStr">
+      <c r="W51" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S51" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T51" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U51" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W51" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>618260</t>
+          <t>620219</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1204874</t>
+          <t>1241591</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>403588</t>
+          <t>408642</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>632967</t>
+          <t>622073</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1071068</t>
+          <t>1063850</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>1855513</t>
+          <t>1751154</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>51,06%</t>
         </is>
       </c>
     </row>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>219954</t>
+          <t>209064</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>393699</t>
+          <t>392900</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6423,12 +6423,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>207446</t>
+          <t>208720</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>278603</t>
+          <t>279100</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>439866</t>
+          <t>460512</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>654186</t>
+          <t>646695</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6521,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>127748</t>
+          <t>128208</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>234791</t>
+          <t>232060</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>127096</t>
+          <t>130309</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>179826</t>
+          <t>179165</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>267564</t>
+          <t>274116</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>392314</t>
+          <t>397369</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>204648</t>
+          <t>189660</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>357687</t>
+          <t>358699</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>179837</t>
+          <t>181263</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>244441</t>
+          <t>244680</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>406047</t>
+          <t>400394</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>581424</t>
+          <t>583656</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>149249</t>
+          <t>148517</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>285778</t>
+          <t>281497</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>189800</t>
+          <t>189651</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>253817</t>
+          <t>253211</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>356553</t>
+          <t>364324</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>522052</t>
+          <t>526895</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>69237</t>
+          <t>63454</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>128038</t>
+          <t>129591</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>110471</t>
+          <t>111265</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>160477</t>
+          <t>161090</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>179447</t>
+          <t>186803</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>277253</t>
+          <t>277502</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70C1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P70C1_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23593</t>
+          <t>31635</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11387</t>
+          <t>18842</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37197</t>
+          <t>48828</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28341</t>
+          <t>30500</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18343</t>
+          <t>19777</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41338</t>
+          <t>46569</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>51934</t>
+          <t>62135</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35614</t>
+          <t>45279</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70282</t>
+          <t>82234</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,84%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28222</t>
+          <t>29076</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14675</t>
+          <t>16155</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45283</t>
+          <t>43341</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15243</t>
+          <t>21314</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>36206</t>
+          <t>40118</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22603</t>
+          <t>26879</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57370</t>
+          <t>61094</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>31,08%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>8627</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13298</t>
+          <t>20296</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14399</t>
+          <t>15935</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24696</t>
+          <t>27851</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>19641</t>
+          <t>24562</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>13500</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34088</t>
+          <t>41850</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12425</t>
+          <t>12383</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29356</t>
+          <t>26616</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14807</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7848</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25233</t>
+          <t>26053</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>27942</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15516</t>
+          <t>16168</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43595</t>
+          <t>43841</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19374</t>
+          <t>19683</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>9362</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34687</t>
+          <t>34773</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11025</t>
+          <t>14154</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19635</t>
+          <t>25630</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>30399</t>
+          <t>33838</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17787</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46847</t>
+          <t>51503</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8623</t>
+          <t>11154</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>4553</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12613</t>
+          <t>13352</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>7969</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15517</t>
+          <t>17420</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>171855</t>
+          <t>196564</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>171855</t>
+          <t>196564</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>171855</t>
+          <t>196564</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>109732</t>
+          <t>117226</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88907</t>
+          <t>92717</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>132652</t>
+          <t>142243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>159535</t>
+          <t>100981</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>106953</t>
+          <t>84841</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>257755</t>
+          <t>119448</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>269268</t>
+          <t>218207</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>212834</t>
+          <t>189221</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>405359</t>
+          <t>246456</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>34,51%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>56074</t>
+          <t>65473</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41715</t>
+          <t>47778</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74934</t>
+          <t>83398</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55911</t>
+          <t>61463</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28512</t>
+          <t>48099</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76260</t>
+          <t>76775</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>111985</t>
+          <t>126935</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>78536</t>
+          <t>106106</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>136497</t>
+          <t>151566</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38620</t>
+          <t>44426</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26068</t>
+          <t>31570</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55706</t>
+          <t>63321</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25159</t>
+          <t>31665</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12007</t>
+          <t>22056</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38724</t>
+          <t>43989</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>63779</t>
+          <t>76091</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44143</t>
+          <t>58339</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85111</t>
+          <t>96804</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>66798</t>
+          <t>75383</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49976</t>
+          <t>55148</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88682</t>
+          <t>97856</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>43466</t>
+          <t>49229</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20736</t>
+          <t>36264</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60800</t>
+          <t>62533</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>110263</t>
+          <t>124612</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>75985</t>
+          <t>101041</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138992</t>
+          <t>148757</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59319</t>
+          <t>68922</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43655</t>
+          <t>49432</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80412</t>
+          <t>92423</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>48836</t>
+          <t>52533</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22629</t>
+          <t>39747</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>67583</t>
+          <t>68729</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>108154</t>
+          <t>121454</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>76886</t>
+          <t>100275</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>136783</t>
+          <t>149341</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>19801</t>
+          <t>24491</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>13805</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35029</t>
+          <t>40230</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19847</t>
+          <t>22265</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>14463</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31067</t>
+          <t>33322</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>39647</t>
+          <t>46756</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24972</t>
+          <t>32972</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56303</t>
+          <t>66914</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>395920</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>395920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>395920</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>352753</t>
+          <t>318136</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>352753</t>
+          <t>318136</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>352753</t>
+          <t>318136</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>703096</t>
+          <t>714056</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>703096</t>
+          <t>714056</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>703096</t>
+          <t>714056</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>149179</t>
+          <t>170729</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>129885</t>
+          <t>147608</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>171703</t>
+          <t>192343</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>86323</t>
+          <t>96323</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>73385</t>
+          <t>82521</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>100356</t>
+          <t>110137</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>235503</t>
+          <t>267052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>210109</t>
+          <t>240046</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>261427</t>
+          <t>296951</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>68700</t>
+          <t>83053</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53018</t>
+          <t>68001</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>83868</t>
+          <t>103521</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>60794</t>
+          <t>69552</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51343</t>
+          <t>56595</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74037</t>
+          <t>82360</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>129494</t>
+          <t>152605</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111628</t>
+          <t>133311</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>149072</t>
+          <t>175108</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>64322</t>
+          <t>77607</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50675</t>
+          <t>62291</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80592</t>
+          <t>96654</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>39174</t>
+          <t>44059</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30595</t>
+          <t>34735</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50866</t>
+          <t>56298</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>103496</t>
+          <t>121666</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86373</t>
+          <t>102201</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>122954</t>
+          <t>143294</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87932</t>
+          <t>99528</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>70570</t>
+          <t>82020</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>107157</t>
+          <t>120014</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>58194</t>
+          <t>65886</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46933</t>
+          <t>52715</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>70991</t>
+          <t>78009</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>146125</t>
+          <t>165413</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>124451</t>
+          <t>145515</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>168863</t>
+          <t>190035</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>59403</t>
+          <t>68226</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45819</t>
+          <t>51936</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76126</t>
+          <t>86056</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>68118</t>
+          <t>76830</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57051</t>
+          <t>64552</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81501</t>
+          <t>91679</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,22 +2837,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>127521</t>
+          <t>145056</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>108288</t>
+          <t>124388</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>146843</t>
+          <t>166385</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -2880,17 +2880,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>29175</t>
+          <t>33889</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19334</t>
+          <t>22445</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40580</t>
+          <t>46534</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>37921</t>
+          <t>44231</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28856</t>
+          <t>34487</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48890</t>
+          <t>55705</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>67096</t>
+          <t>78119</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>54388</t>
+          <t>63863</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>84514</t>
+          <t>94271</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>458711</t>
+          <t>533030</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>458711</t>
+          <t>533030</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>458711</t>
+          <t>533030</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>350523</t>
+          <t>396881</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>350523</t>
+          <t>396881</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>350523</t>
+          <t>396881</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>809235</t>
+          <t>929911</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>809235</t>
+          <t>929911</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>809235</t>
+          <t>929911</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>410646</t>
+          <t>180661</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>239915</t>
+          <t>158837</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>611301</t>
+          <t>201628</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>150427</t>
+          <t>124082</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>121607</t>
+          <t>110308</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>231035</t>
+          <t>139342</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>561073</t>
+          <t>304743</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>376925</t>
+          <t>278071</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>847683</t>
+          <t>333080</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>114379</t>
+          <t>121628</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36289</t>
+          <t>103657</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>177137</t>
+          <t>142703</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>80800</t>
+          <t>92004</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>59503</t>
+          <t>78404</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>94108</t>
+          <t>105208</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>195179</t>
+          <t>213632</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>107147</t>
+          <t>192546</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>255082</t>
+          <t>237970</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>51606</t>
+          <t>57114</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>19665</t>
+          <t>44346</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>81178</t>
+          <t>72161</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>54998</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>36573</t>
+          <t>44676</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>61556</t>
+          <t>66381</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>101519</t>
+          <t>112112</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>53566</t>
+          <t>94912</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>135497</t>
+          <t>129356</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>85106</t>
+          <t>91257</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36526</t>
+          <t>74334</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>133099</t>
+          <t>109448</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>61840</t>
+          <t>68570</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>46110</t>
+          <t>57790</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>75332</t>
+          <t>81213</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>146945</t>
+          <t>159827</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>73329</t>
+          <t>138872</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>193815</t>
+          <t>182757</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>55709</t>
+          <t>60666</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21618</t>
+          <t>47007</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>89118</t>
+          <t>78349</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>65465</t>
+          <t>72215</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>48288</t>
+          <t>60567</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>78664</t>
+          <t>85395</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>121174</t>
+          <t>132881</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>63875</t>
+          <t>112538</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>161719</t>
+          <t>154127</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>30978</t>
+          <t>35500</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10647</t>
+          <t>23977</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>51964</t>
+          <t>50072</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>45060</t>
+          <t>43713</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>33379</t>
+          <t>34328</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>61753</t>
+          <t>54445</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>76039</t>
+          <t>79213</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>39102</t>
+          <t>64776</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>105415</t>
+          <t>97997</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>748424</t>
+          <t>546826</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>748424</t>
+          <t>546826</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>748424</t>
+          <t>546826</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>453505</t>
+          <t>455582</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>453505</t>
+          <t>455582</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>453505</t>
+          <t>455582</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1201929</t>
+          <t>1002408</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1201929</t>
+          <t>1002408</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1201929</t>
+          <t>1002408</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>94991</t>
+          <t>106200</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>80432</t>
+          <t>88436</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>111549</t>
+          <t>123480</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>48008</t>
+          <t>55051</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>40246</t>
+          <t>45882</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>57325</t>
+          <t>65812</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>142999</t>
+          <t>161250</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>126783</t>
+          <t>142184</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>161653</t>
+          <t>180486</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,14%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>59702</t>
+          <t>62497</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>46839</t>
+          <t>49461</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>72585</t>
+          <t>76409</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>41287</t>
+          <t>44577</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>33466</t>
+          <t>36398</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>50944</t>
+          <t>54027</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>100989</t>
+          <t>107074</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>84949</t>
+          <t>91861</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>118210</t>
+          <t>123857</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>32041</t>
+          <t>34669</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>23299</t>
+          <t>26461</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>42306</t>
+          <t>46933</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>24651</t>
+          <t>28204</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>19093</t>
+          <t>21125</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>32431</t>
+          <t>36558</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>56692</t>
+          <t>62874</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>45638</t>
+          <t>50932</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>68263</t>
+          <t>76511</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>47755</t>
+          <t>56561</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>35901</t>
+          <t>43989</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>59934</t>
+          <t>70621</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>37756</t>
+          <t>42574</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>29734</t>
+          <t>34269</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>46680</t>
+          <t>53374</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>85511</t>
+          <t>99135</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>72466</t>
+          <t>83872</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>101278</t>
+          <t>115784</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>45012</t>
+          <t>47443</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>34173</t>
+          <t>36224</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>58159</t>
+          <t>60728</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>30794</t>
+          <t>35035</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>23645</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>38545</t>
+          <t>44025</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>75806</t>
+          <t>82477</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>62423</t>
+          <t>67692</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>90237</t>
+          <t>98578</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>22034</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>14016</t>
+          <t>14324</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>31930</t>
+          <t>33075</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>24643</t>
+          <t>26754</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>17604</t>
+          <t>20442</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>31353</t>
+          <t>35007</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>45446</t>
+          <t>48787</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>36176</t>
+          <t>38330</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>57333</t>
+          <t>62521</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>300304</t>
+          <t>329404</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>300304</t>
+          <t>329404</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>300304</t>
+          <t>329404</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>207139</t>
+          <t>232194</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>207139</t>
+          <t>232194</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>207139</t>
+          <t>232194</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>507443</t>
+          <t>561598</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>507443</t>
+          <t>561598</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>507443</t>
+          <t>561598</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4700,32 +4700,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>6861</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>8744</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>13848</t>
+          <t>15152</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>9521</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>17954</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,49%</t>
         </is>
       </c>
     </row>
@@ -4813,32 +4813,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>7737</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6362</t>
+          <t>7792</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>6934</t>
+          <t>8607</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>5437</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>10816</t>
+          <t>13225</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>34,51%</t>
         </is>
       </c>
     </row>
@@ -4926,32 +4926,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>695</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>5586</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>662</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2314</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -5039,32 +5039,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -5187,32 +5187,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>585</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>595</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>698</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5275,12 +5275,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5300,32 +5300,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4497</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>7667</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -5378,17 +5378,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>17186</t>
+          <t>19151</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>17186</t>
+          <t>19151</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>17186</t>
+          <t>19151</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>34129</t>
+          <t>38317</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>34129</t>
+          <t>38317</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>34129</t>
+          <t>38317</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
@@ -6173,17 +6173,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6243,17 +6243,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6290,32 +6290,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>797666</t>
+          <t>616559</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>620219</t>
+          <t>569631</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1241591</t>
+          <t>665218</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6325,32 +6325,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>478557</t>
+          <t>413798</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>408642</t>
+          <t>382251</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>622073</t>
+          <t>446128</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6360,32 +6360,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>1276223</t>
+          <t>1030356</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1063850</t>
+          <t>974186</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>1751154</t>
+          <t>1084283</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -6403,32 +6403,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>330218</t>
+          <t>365771</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>209064</t>
+          <t>327980</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>392900</t>
+          <t>407489</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6438,32 +6438,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>250568</t>
+          <t>283200</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>208720</t>
+          <t>257127</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>279100</t>
+          <t>309662</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6473,32 +6473,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>580786</t>
+          <t>648971</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>460512</t>
+          <t>599128</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>646695</t>
+          <t>691590</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -6516,32 +6516,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>194108</t>
+          <t>224870</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>128208</t>
+          <t>194549</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>232060</t>
+          <t>252073</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6551,32 +6551,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>153950</t>
+          <t>175524</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>130309</t>
+          <t>152823</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>179165</t>
+          <t>198989</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>348058</t>
+          <t>400395</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>274116</t>
+          <t>364678</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>397369</t>
+          <t>441219</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -6629,32 +6629,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>302981</t>
+          <t>338816</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>189660</t>
+          <t>302745</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>358699</t>
+          <t>378338</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6664,32 +6664,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>217070</t>
+          <t>242881</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>181263</t>
+          <t>218355</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>244680</t>
+          <t>268780</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6699,32 +6699,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>520050</t>
+          <t>581697</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>400394</t>
+          <t>535008</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>583656</t>
+          <t>629366</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -6742,32 +6742,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>238817</t>
+          <t>264940</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>148517</t>
+          <t>234243</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>281497</t>
+          <t>304435</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6777,32 +6777,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>226395</t>
+          <t>252970</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>189651</t>
+          <t>227281</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>253211</t>
+          <t>279162</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6812,32 +6812,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>465212</t>
+          <t>517910</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>364324</t>
+          <t>474301</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>526895</t>
+          <t>560037</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -6855,32 +6855,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>103150</t>
+          <t>120028</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>63454</t>
+          <t>97342</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>129591</t>
+          <t>146686</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6890,32 +6890,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>135805</t>
+          <t>145314</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>111265</t>
+          <t>125897</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>161090</t>
+          <t>166887</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6925,32 +6925,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>238954</t>
+          <t>265342</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>186803</t>
+          <t>237394</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>277502</t>
+          <t>298582</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -6968,17 +6968,17 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>1966940</t>
+          <t>1930984</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>1966940</t>
+          <t>1930984</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>1966940</t>
+          <t>1930984</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7003,17 +7003,17 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>1462345</t>
+          <t>1513687</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>1462345</t>
+          <t>1513687</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>1462345</t>
+          <t>1513687</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7038,17 +7038,17 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>3429285</t>
+          <t>3444671</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>3429285</t>
+          <t>3444671</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3429285</t>
+          <t>3444671</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
